--- a/data/HCA_cluster_distribution_prop.xlsx
+++ b/data/HCA_cluster_distribution_prop.xlsx
@@ -11,47 +11,6 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>CBSA_Cluster</t>
-  </si>
-  <si>
-    <t>CBSAs (n)</t>
-  </si>
-  <si>
-    <t>Institutions (n)</t>
-  </si>
-  <si>
-    <t>Inst. 1 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 2 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 3 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 4 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 5 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 6 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 7 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 8 (%)</t>
-  </si>
-  <si>
-    <t>Inst. 9 (%)</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -395,45 +354,69 @@
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CBSA_Cluster</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CBSAs (n)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Institutions (n)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 1 (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 2 (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 3 (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 4 (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 5 (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 6 (%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 7 (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 8 (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Inst. 9 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -471,7 +454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -509,7 +492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -547,7 +530,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -585,7 +568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -623,7 +606,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -661,7 +644,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -699,7 +682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
